--- a/information.xlsx
+++ b/information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\sync\section_work\Projects\apotheosis-culculator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460AE1BA-1ABC-436A-B2B7-F9B5C261AFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E96DD0A-D96B-4AEC-A30B-125B67AA167A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,9 +59,6 @@
     <t>魔咒线索</t>
   </si>
   <si>
-    <t>#forge:bookshelves</t>
-  </si>
-  <si>
     <t>原版书架</t>
   </si>
   <si>
@@ -137,13 +134,7 @@
     <t>灵魂触摸深暗书架</t>
   </si>
   <si>
-    <t>apotheosis:echoing_shulkshelf</t>
-  </si>
-  <si>
     <t>回响幽匿书架</t>
-  </si>
-  <si>
-    <t>apotheosis:soul_touched_shulkshelf</t>
   </si>
   <si>
     <t>灵魂触摸幽匿书架</t>
@@ -265,6 +256,16 @@
   <si>
     <t>每个方块可以放几个</t>
     <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>#forge:bookshelves</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>apotheosis:echoing_sculkshelf</t>
+  </si>
+  <si>
+    <t>apotheosis:soul_touched_sculkshelf</t>
   </si>
 </sst>
 </file>
@@ -272,11 +273,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="178" formatCode="\+General;\-General;General"/>
-    <numFmt numFmtId="179" formatCode="\+0.00;\-0.00;"/>
-    <numFmt numFmtId="180" formatCode="\+0.00&quot;%&quot;;\-0.00&quot;%&quot;;"/>
+    <numFmt numFmtId="176" formatCode="\+General;\-General;General"/>
+    <numFmt numFmtId="177" formatCode="\+0.00;\-0.00;"/>
+    <numFmt numFmtId="178" formatCode="\+0.00&quot;%&quot;;\-0.00&quot;%&quot;;"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -432,6 +433,13 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="黑体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -489,26 +497,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -517,16 +525,16 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -535,28 +543,31 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="177" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="178" fontId="16" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="17" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="178" fontId="17" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="18" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="178" fontId="18" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="19" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="19" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="20" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2403,17 +2414,17 @@
         <v>7</v>
       </c>
       <c r="J1" s="22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="13"/>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>9</v>
       </c>
       <c r="D2" s="15">
         <v>1</v>
@@ -2437,6 +2448,7 @@
     rectification:"&amp;IF(ISBLANK(G2),0,G2)&amp;",
     arcana:"&amp;IF(ISBLANK(H2),0,H2)&amp;",
     clues:"&amp;IF(ISBLANK(I2),0,I2)&amp;",
+    blockCapacity:"&amp;IF(ISBLANK(J2),1,J2)&amp;",
 },"</f>
         <v>{
     id:"#forge:bookshelves",
@@ -2446,6 +2458,7 @@
     rectification:0,
     arcana:0,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L2" s="19" t="str">
@@ -2456,10 +2469,10 @@
     <row r="3" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13"/>
       <c r="B3" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>10</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>11</v>
       </c>
       <c r="D3" s="15">
         <v>1.5</v>
@@ -2477,7 +2490,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="19" t="str">
-        <f>"{
+        <f t="shared" ref="K3:K35" si="1">"{
     id:"""&amp;B3&amp;""",
     level:"&amp;IF(ISBLANK(D3),0,D3)&amp;",
     maxLevel:"&amp;IF(ISBLANK(E3),0,E3)&amp;",
@@ -2485,6 +2498,7 @@
     rectification:"&amp;IF(ISBLANK(G3),0,G3)&amp;",
     arcana:"&amp;IF(ISBLANK(H3),0,H3)&amp;",
     clues:"&amp;IF(ISBLANK(I3),0,I3)&amp;",
+    blockCapacity:"&amp;IF(ISBLANK(J3),1,J3)&amp;",
 },"</f>
         <v>{
     id:"apotheosis:hellshelf",
@@ -2494,6 +2508,7 @@
     rectification:0,
     arcana:0,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L3" s="19" t="str">
@@ -2504,10 +2519,10 @@
     <row r="4" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13"/>
       <c r="B4" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>12</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>13</v>
       </c>
       <c r="D4" s="15">
         <v>1.75</v>
@@ -2525,15 +2540,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="19" t="str">
-        <f>"{
-    id:"""&amp;B4&amp;""",
-    level:"&amp;IF(ISBLANK(D4),0,D4)&amp;",
-    maxLevel:"&amp;IF(ISBLANK(E4),0,E4)&amp;",
-    quanta:"&amp;IF(ISBLANK(F4),0,F4)&amp;",
-    rectification:"&amp;IF(ISBLANK(G4),0,G4)&amp;",
-    arcana:"&amp;IF(ISBLANK(H4),0,H4)&amp;",
-    clues:"&amp;IF(ISBLANK(I4),0,I4)&amp;",
-},"</f>
+        <f t="shared" si="1"/>
         <v>{
     id:"apotheosis:infused_hellshelf",
     level:1.75,
@@ -2542,6 +2549,7 @@
     rectification:0,
     arcana:0,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L4" s="19" t="str">
@@ -2552,10 +2560,10 @@
     <row r="5" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13"/>
       <c r="B5" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>15</v>
       </c>
       <c r="D5" s="15">
         <v>4</v>
@@ -2575,15 +2583,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="19" t="str">
-        <f>"{
-    id:"""&amp;B5&amp;""",
-    level:"&amp;IF(ISBLANK(D5),0,D5)&amp;",
-    maxLevel:"&amp;IF(ISBLANK(E5),0,E5)&amp;",
-    quanta:"&amp;IF(ISBLANK(F5),0,F5)&amp;",
-    rectification:"&amp;IF(ISBLANK(G5),0,G5)&amp;",
-    arcana:"&amp;IF(ISBLANK(H5),0,H5)&amp;",
-    clues:"&amp;IF(ISBLANK(I5),0,I5)&amp;",
-},"</f>
+        <f t="shared" si="1"/>
         <v>{
     id:"apotheosis:blazing_hellshelf",
     level:4,
@@ -2592,6 +2592,7 @@
     rectification:0,
     arcana:0,
     clues:-1,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L5" s="19" t="str">
@@ -2602,10 +2603,10 @@
     <row r="6" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
       <c r="B6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>17</v>
       </c>
       <c r="D6" s="15">
         <v>2</v>
@@ -2625,15 +2626,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="19" t="str">
-        <f>"{
-    id:"""&amp;B6&amp;""",
-    level:"&amp;IF(ISBLANK(D6),0,D6)&amp;",
-    maxLevel:"&amp;IF(ISBLANK(E6),0,E6)&amp;",
-    quanta:"&amp;IF(ISBLANK(F6),0,F6)&amp;",
-    rectification:"&amp;IF(ISBLANK(G6),0,G6)&amp;",
-    arcana:"&amp;IF(ISBLANK(H6),0,H6)&amp;",
-    clues:"&amp;IF(ISBLANK(I6),0,I6)&amp;",
-},"</f>
+        <f t="shared" si="1"/>
         <v>{
     id:"apotheosis:glowing_hellshelf",
     level:2,
@@ -2642,6 +2635,7 @@
     rectification:0,
     arcana:4,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L6" s="19" t="str">
@@ -2652,10 +2646,10 @@
     <row r="7" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
       <c r="B7" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>18</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>19</v>
       </c>
       <c r="D7" s="15">
         <v>1.5</v>
@@ -2673,15 +2667,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="19" t="str">
-        <f t="shared" ref="K7:K35" si="1">"{
-    id:"""&amp;B7&amp;""",
-    level:"&amp;IF(ISBLANK(D7),0,D7)&amp;",
-    maxLevel:"&amp;IF(ISBLANK(E7),0,E7)&amp;",
-    quanta:"&amp;IF(ISBLANK(F7),0,F7)&amp;",
-    rectification:"&amp;IF(ISBLANK(G7),0,G7)&amp;",
-    arcana:"&amp;IF(ISBLANK(H7),0,H7)&amp;",
-    clues:"&amp;IF(ISBLANK(I7),0,I7)&amp;",
-},"</f>
+        <f t="shared" si="1"/>
         <v>{
     id:"apotheosis:seashelf",
     level:1.5,
@@ -2690,6 +2676,7 @@
     rectification:0,
     arcana:2,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L7" s="19" t="str">
@@ -2700,10 +2687,10 @@
     <row r="8" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13"/>
       <c r="B8" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>20</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>21</v>
       </c>
       <c r="D8" s="15">
         <v>1.75</v>
@@ -2730,6 +2717,7 @@
     rectification:0,
     arcana:1.75,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L8" s="19" t="str">
@@ -2740,10 +2728,10 @@
     <row r="9" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13"/>
       <c r="B9" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>22</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>23</v>
       </c>
       <c r="D9" s="15">
         <v>2</v>
@@ -2772,6 +2760,7 @@
     rectification:0,
     arcana:2,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L9" s="19" t="str">
@@ -2782,10 +2771,10 @@
     <row r="10" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13"/>
       <c r="B10" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>24</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>25</v>
       </c>
       <c r="D10" s="15">
         <v>3</v>
@@ -2814,6 +2803,7 @@
     rectification:-5,
     arcana:10,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L10" s="19" t="str">
@@ -2824,10 +2814,10 @@
     <row r="11" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13"/>
       <c r="B11" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>26</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>27</v>
       </c>
       <c r="D11" s="15">
         <v>1</v>
@@ -2852,6 +2842,7 @@
     rectification:0,
     arcana:0,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L11" s="19" t="str">
@@ -2862,10 +2853,10 @@
     <row r="12" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13"/>
       <c r="B12" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>28</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>29</v>
       </c>
       <c r="D12" s="15">
         <v>2.5</v>
@@ -2894,6 +2885,7 @@
     rectification:0,
     arcana:5,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L12" s="19" t="str">
@@ -2904,10 +2896,10 @@
     <row r="13" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13"/>
       <c r="B13" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>30</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>31</v>
       </c>
       <c r="D13" s="15">
         <v>2.5</v>
@@ -2934,6 +2926,7 @@
     rectification:0,
     arcana:15,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L13" s="19" t="str">
@@ -2944,10 +2937,10 @@
     <row r="14" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13"/>
       <c r="B14" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="D14" s="15">
         <v>2.5</v>
@@ -2974,6 +2967,7 @@
     rectification:0,
     arcana:0,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L14" s="19" t="str">
@@ -2984,10 +2978,10 @@
     <row r="15" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13"/>
       <c r="B15" s="13" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" s="15">
         <v>5</v>
@@ -3011,27 +3005,28 @@
       <c r="K15" s="19" t="str">
         <f t="shared" si="1"/>
         <v>{
-    id:"apotheosis:echoing_shulkshelf",
+    id:"apotheosis:echoing_sculkshelf",
     level:5,
     maxLevel:40,
     quanta:5,
     rectification:0,
     arcana:15,
     clues:1,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L15" s="19" t="str">
         <f t="shared" si="0"/>
-        <v>"apotheosis:echoing_shulkshelf":"回响幽匿书架",</v>
+        <v>"apotheosis:echoing_sculkshelf":"回响幽匿书架",</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13"/>
       <c r="B16" s="13" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D16" s="15">
         <v>5</v>
@@ -3055,27 +3050,28 @@
       <c r="K16" s="19" t="str">
         <f t="shared" si="1"/>
         <v>{
-    id:"apotheosis:soul_touched_shulkshelf",
+    id:"apotheosis:soul_touched_sculkshelf",
     level:5,
     maxLevel:40,
     quanta:15,
     rectification:5,
     arcana:5,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L16" s="19" t="str">
         <f t="shared" si="0"/>
-        <v>"apotheosis:soul_touched_shulkshelf":"灵魂触摸幽匿书架",</v>
+        <v>"apotheosis:soul_touched_sculkshelf":"灵魂触摸幽匿书架",</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13"/>
       <c r="B17" s="13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D17" s="15">
         <v>2.5</v>
@@ -3104,6 +3100,7 @@
     rectification:0,
     arcana:5,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L17" s="19" t="str">
@@ -3114,10 +3111,10 @@
     <row r="18" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13"/>
       <c r="B18" s="13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D18" s="15">
         <v>10</v>
@@ -3142,6 +3139,7 @@
     rectification:0,
     arcana:0,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L18" s="19" t="str">
@@ -3152,10 +3150,10 @@
     <row r="19" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13"/>
       <c r="B19" s="13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D19" s="15">
         <v>5</v>
@@ -3184,6 +3182,7 @@
     rectification:0,
     arcana:7.5,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L19" s="19" t="str">
@@ -3194,10 +3193,10 @@
     <row r="20" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="13"/>
       <c r="B20" s="13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D20" s="15">
         <v>-15</v>
@@ -3222,6 +3221,7 @@
     rectification:0,
     arcana:0,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L20" s="19" t="str">
@@ -3232,10 +3232,10 @@
     <row r="21" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="13"/>
       <c r="B21" s="13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D21" s="15">
         <v>-1</v>
@@ -3260,6 +3260,7 @@
     rectification:0,
     arcana:0,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L21" s="19" t="str">
@@ -3270,10 +3271,10 @@
     <row r="22" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="13"/>
       <c r="B22" s="13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D22" s="15">
         <v>-1.5</v>
@@ -3298,6 +3299,7 @@
     rectification:0,
     arcana:7.5,
     clues:0,
+    blockCapacity:1,
 },</v>
       </c>
       <c r="L22" s="19" t="str">
@@ -3308,10 +3310,10 @@
     <row r="23" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="13"/>
       <c r="B23" s="13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
@@ -3325,16 +3327,7 @@
         <v>1</v>
       </c>
       <c r="K23" s="19" t="str">
-        <f>"{
-    id:"""&amp;B23&amp;""",
-    level:"&amp;IF(ISBLANK(D23),0,D23)&amp;",
-    maxLevel:"&amp;IF(ISBLANK(E23),0,E23)&amp;",
-    quanta:"&amp;IF(ISBLANK(F23),0,F23)&amp;",
-    rectification:"&amp;IF(ISBLANK(G23),0,G23)&amp;",
-    arcana:"&amp;IF(ISBLANK(H23),0,H23)&amp;",
-    clues:"&amp;IF(ISBLANK(I23),0,I23)&amp;",
-    blockCapacity:"&amp;IF(ISBLANK(J23),0,J23)&amp;",
-},"</f>
+        <f t="shared" si="1"/>
         <v>{
     id:"apotheosis:rectifier",
     level:0,
@@ -3354,10 +3347,10 @@
     <row r="24" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
       <c r="B24" s="13" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
@@ -3371,16 +3364,7 @@
         <v>1</v>
       </c>
       <c r="K24" s="19" t="str">
-        <f t="shared" ref="K24:K35" si="2">"{
-    id:"""&amp;B24&amp;""",
-    level:"&amp;IF(ISBLANK(D24),0,D24)&amp;",
-    maxLevel:"&amp;IF(ISBLANK(E24),0,E24)&amp;",
-    quanta:"&amp;IF(ISBLANK(F24),0,F24)&amp;",
-    rectification:"&amp;IF(ISBLANK(G24),0,G24)&amp;",
-    arcana:"&amp;IF(ISBLANK(H24),0,H24)&amp;",
-    clues:"&amp;IF(ISBLANK(I24),0,I24)&amp;",
-    blockCapacity:"&amp;IF(ISBLANK(J24),0,J24)&amp;",
-},"</f>
+        <f t="shared" si="1"/>
         <v>{
     id:"apotheosis:rectifier_t2",
     level:0,
@@ -3400,10 +3384,10 @@
     <row r="25" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13"/>
       <c r="B25" s="13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
@@ -3417,7 +3401,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>{
     id:"apotheosis:rectifier_t3",
     level:0,
@@ -3437,10 +3421,10 @@
     <row r="26" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="13"/>
       <c r="B26" s="13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D26" s="15"/>
       <c r="E26" s="15"/>
@@ -3454,7 +3438,7 @@
         <v>1</v>
       </c>
       <c r="K26" s="19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>{
     id:"apotheosis:sightshelf",
     level:0,
@@ -3474,10 +3458,10 @@
     <row r="27" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="13"/>
       <c r="B27" s="13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
@@ -3491,7 +3475,7 @@
         <v>1</v>
       </c>
       <c r="K27" s="19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>{
     id:"apotheosis:sightshelf_t2",
     level:0,
@@ -3511,10 +3495,10 @@
     <row r="28" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
       <c r="B28" s="13" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
@@ -3528,7 +3512,7 @@
         <v>1</v>
       </c>
       <c r="K28" s="19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>{
     id:"#forge:heads",
     level:0,
@@ -3548,10 +3532,10 @@
     <row r="29" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="13"/>
       <c r="B29" s="13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
@@ -3565,7 +3549,7 @@
         <v>1</v>
       </c>
       <c r="K29" s="19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>{
     id:"minecraft:wither_skeleton_skull",
     level:0,
@@ -3585,10 +3569,10 @@
     <row r="30" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="13"/>
       <c r="B30" s="13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D30" s="15"/>
       <c r="E30" s="15"/>
@@ -3606,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>{
     id:"occultism:sprit_attuned_crystal",
     level:0,
@@ -3626,10 +3610,10 @@
     <row r="31" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="13"/>
       <c r="B31" s="13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D31" s="15">
         <v>3.5</v>
@@ -3647,7 +3631,7 @@
         <v>1</v>
       </c>
       <c r="K31" s="19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>{
     id:"ars_nouveau:enchanting_apparatus",
     level:3.5,
@@ -3667,10 +3651,10 @@
     <row r="32" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="13"/>
       <c r="B32" s="13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D32" s="15">
         <v>3.5</v>
@@ -3688,7 +3672,7 @@
         <v>1</v>
       </c>
       <c r="K32" s="19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>{
     id:"ars_nouveau:arcane_core",
     level:3.5,
@@ -3708,10 +3692,10 @@
     <row r="33" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
       <c r="B33" s="13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D33" s="15">
         <v>1</v>
@@ -3731,7 +3715,7 @@
         <v>1</v>
       </c>
       <c r="K33" s="19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>{
     id:"ars_nouveau:arcane_pedestal",
     level:1,
@@ -3751,10 +3735,10 @@
     <row r="34" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="13"/>
       <c r="B34" s="13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D34" s="15"/>
       <c r="E34" s="15"/>
@@ -3768,7 +3752,7 @@
         <v>4</v>
       </c>
       <c r="K34" s="19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>{
     id:"#minecraft:candles",
     level:0,
@@ -3788,10 +3772,10 @@
     <row r="35" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="13"/>
       <c r="B35" s="13" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="15"/>
@@ -3805,7 +3789,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="19" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>{
     id:"minecraft:amethyst_cluster",
     level:0,
